--- a/docs/隔壁-迭代计划.xlsx
+++ b/docs/隔壁-迭代计划.xlsx
@@ -13,7 +13,7 @@
     <sheet name="实验指标" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">迭代清单!$A$1:$L$18</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">迭代清单!$A$1:$L$20</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="153">
   <si>
     <t xml:space="preserve">隔壁 · 迭代计划</t>
   </si>
@@ -248,14 +248,18 @@
     <t xml:space="preserve">上线前完成隐私处理与合规确认</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">代码部分已完成（</t>
-    </r>
+    <t xml:space="preserve">代码部分已完成（v4）：选址吸附到最近城市并随机偏移，只显示到 0.1°。审图号要求待专业人士确认。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">访客记录与“留言 → 回复”闭环</t>
+  </si>
+  <si>
+    <t xml:space="preserve">房间被看了，房主却不知道；缺少回访理由</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自动记录访客；由 Bit 汇总成一句话（例：今晚 @pixelmo 来过，玩了你的游戏，在黑板上留了言）；房主可直接回复，回复通知到对方</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -263,7 +267,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">v4</t>
+      <t xml:space="preserve">QQ </t>
     </r>
     <r>
       <rPr>
@@ -271,8 +275,13 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）：选址吸附到最近城市并随机偏移，只显示到 </t>
-    </r>
+      <t xml:space="preserve">空间“谁看过我”；文稿“首次有效反馈等待时间”“重复交流”</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">首次回应的等待时间；重复互动的人员组合</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -280,7 +289,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0.1°</t>
+      <t xml:space="preserve">v4</t>
     </r>
     <r>
       <rPr>
@@ -288,19 +297,8 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">。审图号要求待专业人士确认。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">访客记录与“留言 → 回复”闭环</t>
-  </si>
-  <si>
-    <t xml:space="preserve">房间被看了，房主却不知道；缺少回访理由</t>
-  </si>
-  <si>
-    <t xml:space="preserve">自动记录访客；由 Bit 汇总成一句话（例：今晚 @pixelmo 来过，玩了你的游戏，在黑板上留了言）；房主可直接回复，回复通知到对方</t>
-  </si>
-  <si>
+      <t xml:space="preserve">：访客自动记录；</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -308,7 +306,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">QQ </t>
+      <t xml:space="preserve">Bit </t>
     </r>
     <r>
       <rPr>
@@ -316,11 +314,17 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">空间“谁看过我”；文稿“首次有效反馈等待时间”“重复交流”</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">首次回应的等待时间；重复互动的人员组合</t>
+      <t xml:space="preserve">和访客簿汇总新访客与留言；房主可直接回复；对方下次打开时在“动态”里看到（站内提醒，无推送）。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">单文件作品托管</t>
+  </si>
+  <si>
+    <t xml:space="preserve">绑定外部网址很脆弱，很多网站禁止被嵌入，实验时一定有人卡住</t>
+  </si>
+  <si>
+    <t xml:space="preserve">支持上传或粘贴单个 HTML 文件，由平台托管；作品一定能打开，可接入 SDK 与物件同步；审核有抓手</t>
   </si>
   <si>
     <r>
@@ -330,7 +334,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">v4</t>
+      <t xml:space="preserve">AI </t>
     </r>
     <r>
       <rPr>
@@ -338,7 +342,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">：访客自动记录；</t>
+      <t xml:space="preserve">做出来的作品大多是单个 </t>
     </r>
     <r>
       <rPr>
@@ -347,7 +351,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Bit </t>
+      <t xml:space="preserve">HTML </t>
     </r>
     <r>
       <rPr>
@@ -355,17 +359,11 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">和访客簿汇总新访客与留言；房主可直接回复；对方下次打开时在“动态”里看到（站内提醒，无推送）。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">单文件作品托管</t>
-  </si>
-  <si>
-    <t xml:space="preserve">绑定外部网址很脆弱，很多网站禁止被嵌入，实验时一定有人卡住</t>
-  </si>
-  <si>
-    <t xml:space="preserve">支持上传或粘贴单个 HTML 文件，由平台托管；作品一定能打开，可接入 SDK 与物件同步；审核有抓手</t>
+      <t xml:space="preserve">文件</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">作品成功在房间内打开的比例</t>
   </si>
   <si>
     <r>
@@ -375,7 +373,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">AI </t>
+      <t xml:space="preserve">v4</t>
     </r>
     <r>
       <rPr>
@@ -383,7 +381,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">做出来的作品大多是单个 </t>
+      <t xml:space="preserve">：上传或粘贴单个 </t>
     </r>
     <r>
       <rPr>
@@ -392,7 +390,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">HTML </t>
+      <t xml:space="preserve">HTML</t>
     </r>
     <r>
       <rPr>
@@ -400,13 +398,8 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">文件</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">作品成功在房间内打开的比例</t>
-  </si>
-  <si>
+      <t xml:space="preserve">（≤</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -414,7 +407,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">v4</t>
+      <t xml:space="preserve">200 KB</t>
     </r>
     <r>
       <rPr>
@@ -422,7 +415,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">：上传或粘贴单个 </t>
+      <t xml:space="preserve">），在隔离沙箱中运行，可接 </t>
     </r>
     <r>
       <rPr>
@@ -431,7 +424,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">HTML</t>
+      <t xml:space="preserve">SDK</t>
     </r>
     <r>
       <rPr>
@@ -439,8 +432,25 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（≤</t>
-    </r>
+      <t xml:space="preserve">。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">账号与云端存储</t>
+  </si>
+  <si>
+    <t xml:space="preserve">所有数据只存在浏览器本地，无法多人实验</t>
+  </si>
+  <si>
+    <t xml:space="preserve">账号体系；房间、留言、访客数据存到云端</t>
+  </si>
+  <si>
+    <t xml:space="preserve">开放工作室实验的前提</t>
+  </si>
+  <si>
+    <t xml:space="preserve">实验可多人运行</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -448,7 +458,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">200 KB</t>
+      <t xml:space="preserve">v4</t>
     </r>
     <r>
       <rPr>
@@ -456,7 +466,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">），在隔离沙箱中运行，可接 </t>
+      <t xml:space="preserve">：用 </t>
     </r>
     <r>
       <rPr>
@@ -465,7 +475,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">SDK</t>
+      <t xml:space="preserve">claude.ai </t>
     </r>
     <r>
       <rPr>
@@ -473,23 +483,23 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">账号与云端存储</t>
-  </si>
-  <si>
-    <t xml:space="preserve">所有数据只存在浏览器本地，无法多人实验</t>
-  </si>
-  <si>
-    <t xml:space="preserve">账号体系；房间、留言、访客数据存到云端</t>
-  </si>
-  <si>
-    <t xml:space="preserve">开放工作室实验的前提</t>
-  </si>
-  <si>
-    <t xml:space="preserve">实验可多人运行</t>
+      <t xml:space="preserve">账号作为身份；数据存在页面的共享数据库，每人只能写自己的房间、留言和访客记录。参与者需在分享菜单设为“参与者”。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">房间分享卡片</t>
+  </si>
+  <si>
+    <t xml:space="preserve">种子用户邀请与二次传播缺少载体</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自动生成房间截图，带城市和门牌号，适合发微信和小红书</t>
+  </si>
+  <si>
+    <t xml:space="preserve">种子用户邀请与二次传播</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过分享卡片进入的新访客</t>
   </si>
   <si>
     <r>
@@ -507,7 +517,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">：用 </t>
+      <t xml:space="preserve">：</t>
     </r>
     <r>
       <rPr>
@@ -516,7 +526,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">claude.ai </t>
+      <t xml:space="preserve">1080×1440 </t>
     </r>
     <r>
       <rPr>
@@ -524,23 +534,8 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">账号作为身份；数据存在页面的共享数据库，每人只能写自己的房间、留言和访客记录。参与者需在分享菜单设为“参与者”。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">房间分享卡片</t>
-  </si>
-  <si>
-    <t xml:space="preserve">种子用户邀请与二次传播缺少载体</t>
-  </si>
-  <si>
-    <t xml:space="preserve">自动生成房间截图，带城市和门牌号，适合发微信和小红书</t>
-  </si>
-  <si>
-    <t xml:space="preserve">种子用户邀请与二次传播</t>
-  </si>
-  <si>
-    <t xml:space="preserve">通过分享卡片进入的新访客</t>
+      <t xml:space="preserve">卡片，可保存图片、复制直达房间的链接。</t>
+    </r>
   </si>
   <si>
     <r>
@@ -550,7 +545,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">v4</t>
+      <t xml:space="preserve">P1 </t>
     </r>
     <r>
       <rPr>
@@ -558,8 +553,25 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">：</t>
-    </r>
+      <t xml:space="preserve">实验中</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">物件收藏与改编</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不创作的人缺少参与方式；物件的收藏意义来自主人的表达，所以物件要能被主人改成自己的样子</t>
+  </si>
+  <si>
+    <t xml:space="preserve">收藏：把喜欢的物件放进自己房间的展台，保留原作者署名，访客点开可链回作者。改编：复制一份成自己的版本（托管作品一并复制），署名和改编链一直保留。作者能在访客簿看到被收藏、被改编的次数。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">豆瓣式标记与策展；文稿“消费者转化为生产者”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">收藏或策展行为的人数占比</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -567,7 +579,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1080×1440 </t>
+      <t xml:space="preserve">v5</t>
     </r>
     <r>
       <rPr>
@@ -575,8 +587,23 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">卡片，可保存图片、复制直达房间的链接。</t>
-    </r>
+      <t xml:space="preserve">：收藏品展台、改编、署名与改编链、作者端提醒。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">主题周：“理想中的深夜小店”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">陌生人缺少共同对象；空间里缺少持续发生的事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全员布置同一主题的房间；地球上点亮一张主题地图；结束后把活动归档</t>
+  </si>
+  <si>
+    <t xml:space="preserve">文稿从豆瓣得出的“共同对象”；阿尔法城之问：空间里会持续发生什么</t>
+  </si>
+  <si>
+    <t xml:space="preserve">第二、三周重复互动的人员组合</t>
   </si>
   <si>
     <r>
@@ -586,7 +613,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">P1 </t>
+      <t xml:space="preserve">v5</t>
     </r>
     <r>
       <rPr>
@@ -594,38 +621,8 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">实验中</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">物件收藏与改编</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不创作的人缺少参与方式；从看客到作者的路径太重</t>
-  </si>
-  <si>
-    <t xml:space="preserve">收藏：把喜欢的物件放进自己的房间，保留原作者署名，访客点开可链回作者。改编：允许复制一份改成自己的版本，形成改编链条</t>
-  </si>
-  <si>
-    <t xml:space="preserve">豆瓣式标记与策展；文稿“消费者转化为生产者”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">收藏或策展行为的人数占比</t>
-  </si>
-  <si>
-    <t xml:space="preserve">主题周：“理想中的深夜小店”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">陌生人缺少共同对象；空间里缺少持续发生的事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">全员布置同一主题的房间；地球上点亮一张主题地图；结束后把活动归档</t>
-  </si>
-  <si>
-    <t xml:space="preserve">文稿从豆瓣得出的“共同对象”；阿尔法城之问：空间里会持续发生什么</t>
-  </si>
-  <si>
-    <t xml:space="preserve">第二、三周重复互动的人员组合</t>
+      <t xml:space="preserve">：每周自动轮换主题；参加的房间在地球上亮灯、其余变暗；往期归档。当前部分参与者是演示数据。</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">平铺的“物件流”作为发现入口</t>
@@ -658,45 +655,45 @@
   <si>
     <r>
       <rPr>
-        <b val="true"/>
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Agent </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">v5</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">从“陪聊”改为“转达”</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">访客可能只和 Bit 聊天，关系被机器人截住</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t xml:space="preserve">：首页“逛物件流”；分类筛选；站内直接试玩；收藏、改编、当场给作者留一句话。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Bit </t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">Agent </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="10"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">负责接待、介绍作品，并把访客引向房主：帮忙留言、预约、提醒房主回复，不替房主社交</t>
-    </r>
+      <t xml:space="preserve">从“陪聊”改为“转达”</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">访客可能只和 Bit 聊天，关系被机器人截住</t>
   </si>
   <si>
     <r>
@@ -706,7 +703,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Agent </t>
+      <t xml:space="preserve">Bit </t>
     </r>
     <r>
       <rPr>
@@ -714,11 +711,8 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">是中介，不替代人与人的关系</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">首次回应的等待时间</t>
+      <t xml:space="preserve">负责接待、介绍作品，并把访客引向房主：帮忙留言、预约、提醒房主回复，不替房主社交</t>
+    </r>
   </si>
   <si>
     <r>
@@ -728,7 +722,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">P2 </t>
+      <t xml:space="preserve">Agent </t>
     </r>
     <r>
       <rPr>
@@ -736,6 +730,81 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">是中介，不替代人与人的关系</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">首次回应的等待时间</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bit </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改为接待与转达：留言、预约、提醒回复（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">小时限一次）；房主端汇总待回复。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">有信号后</t>
     </r>
   </si>
@@ -795,6 +864,49 @@
   </si>
   <si>
     <t xml:space="preserve">更炫的特效</t>
+  </si>
+  <si>
+    <t xml:space="preserve">物件外观轻定制</t>
+  </si>
+  <si>
+    <t xml:space="preserve">物件只能摆放，主人没法表达自己；没有表达，收藏就没有意义</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每件作品物件可选主题色，展示屏和街机会换成这个颜色；改编的作品可以先从换色开始。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">讨论中对“物件是否能自定义”的判断：收藏的意义在于主人的表达</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有换色或改名的作品物件占比</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：已上线主题色。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">自定义物件外壳</t>
+  </si>
+  <si>
+    <t xml:space="preserve">允许用户为物件上传自己的贴图或简单模型，让物件本身成为原创表达；需要体积限制与审核。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">依赖前面的收藏与改编机制先被验证</t>
   </si>
   <si>
     <t xml:space="preserve">文稿里的问题</t>
@@ -1100,7 +1212,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1205,7 +1317,7 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1231,6 +1343,14 @@
     </xf>
     <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1278,7 +1398,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="13">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1360,40 +1480,12 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF006100"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9C5700"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <color rgb="FF9C5700"/>
-      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
@@ -1401,12 +1493,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
@@ -1424,7 +1510,7 @@
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF9C0006"/>
+      <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
@@ -1466,9 +1552,9 @@
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF006100"/>
+      <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF9C5700"/>
+      <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF2A2140"/>
@@ -1707,19 +1793,19 @@
         <v>9</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF(迭代清单!$B$2:$B$18,A5)</f>
+        <f aca="false">COUNTIF(迭代清单!$B$2:$B$20,A5)</f>
         <v>5</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(迭代清单!$B$2:$B$18,A5,迭代清单!$H$2:$H$18,"已完成")</f>
+        <f aca="false">COUNTIFS(迭代清单!$B$2:$B$20,A5,迭代清单!$H$2:$H$20,"已完成")</f>
         <v>4</v>
       </c>
       <c r="D5" s="6" t="n">
-        <f aca="false">COUNTIFS(迭代清单!$B$2:$B$18,A5,迭代清单!$H$2:$H$18,"进行中")</f>
+        <f aca="false">COUNTIFS(迭代清单!$B$2:$B$20,A5,迭代清单!$H$2:$H$20,"进行中")</f>
         <v>1</v>
       </c>
       <c r="E5" s="6" t="n">
-        <f aca="false">COUNTIFS(迭代清单!$B$2:$B$18,A5,迭代清单!$H$2:$H$18,"未开始")</f>
+        <f aca="false">COUNTIFS(迭代清单!$B$2:$B$20,A5,迭代清单!$H$2:$H$20,"未开始")</f>
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
@@ -1735,24 +1821,24 @@
         <v>11</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF(迭代清单!$B$2:$B$18,A6)</f>
-        <v>4</v>
+        <f aca="false">COUNTIF(迭代清单!$B$2:$B$20,A6)</f>
+        <v>5</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(迭代清单!$B$2:$B$18,A6,迭代清单!$H$2:$H$18,"已完成")</f>
+        <f aca="false">COUNTIFS(迭代清单!$B$2:$B$20,A6,迭代清单!$H$2:$H$20,"已完成")</f>
+        <v>5</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <f aca="false">COUNTIFS(迭代清单!$B$2:$B$20,A6,迭代清单!$H$2:$H$20,"进行中")</f>
         <v>0</v>
       </c>
-      <c r="D6" s="6" t="n">
-        <f aca="false">COUNTIFS(迭代清单!$B$2:$B$18,A6,迭代清单!$H$2:$H$18,"进行中")</f>
+      <c r="E6" s="6" t="n">
+        <f aca="false">COUNTIFS(迭代清单!$B$2:$B$20,A6,迭代清单!$H$2:$H$20,"未开始")</f>
         <v>0</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <f aca="false">COUNTIFS(迭代清单!$B$2:$B$18,A6,迭代清单!$H$2:$H$18,"未开始")</f>
-        <v>4</v>
       </c>
       <c r="F6" s="7" t="n">
         <f aca="false">IF(B6=0,"",C6/B6)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>12</v>
@@ -1763,20 +1849,20 @@
         <v>13</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIF(迭代清单!$B$2:$B$18,A7)</f>
-        <v>5</v>
+        <f aca="false">COUNTIF(迭代清单!$B$2:$B$20,A7)</f>
+        <v>6</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIFS(迭代清单!$B$2:$B$18,A7,迭代清单!$H$2:$H$18,"已完成")</f>
+        <f aca="false">COUNTIFS(迭代清单!$B$2:$B$20,A7,迭代清单!$H$2:$H$20,"已完成")</f>
         <v>0</v>
       </c>
       <c r="D7" s="6" t="n">
-        <f aca="false">COUNTIFS(迭代清单!$B$2:$B$18,A7,迭代清单!$H$2:$H$18,"进行中")</f>
+        <f aca="false">COUNTIFS(迭代清单!$B$2:$B$20,A7,迭代清单!$H$2:$H$20,"进行中")</f>
         <v>0</v>
       </c>
       <c r="E7" s="6" t="n">
-        <f aca="false">COUNTIFS(迭代清单!$B$2:$B$18,A7,迭代清单!$H$2:$H$18,"未开始")</f>
-        <v>5</v>
+        <f aca="false">COUNTIFS(迭代清单!$B$2:$B$20,A7,迭代清单!$H$2:$H$20,"未开始")</f>
+        <v>6</v>
       </c>
       <c r="F7" s="7" t="n">
         <f aca="false">IF(B7=0,"",C7/B7)</f>
@@ -1791,19 +1877,19 @@
         <v>15</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">COUNTIF(迭代清单!$B$2:$B$18,A8)</f>
+        <f aca="false">COUNTIF(迭代清单!$B$2:$B$20,A8)</f>
         <v>3</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">COUNTIFS(迭代清单!$B$2:$B$18,A8,迭代清单!$H$2:$H$18,"已完成")</f>
+        <f aca="false">COUNTIFS(迭代清单!$B$2:$B$20,A8,迭代清单!$H$2:$H$20,"已完成")</f>
         <v>0</v>
       </c>
       <c r="D8" s="6" t="n">
-        <f aca="false">COUNTIFS(迭代清单!$B$2:$B$18,A8,迭代清单!$H$2:$H$18,"进行中")</f>
+        <f aca="false">COUNTIFS(迭代清单!$B$2:$B$20,A8,迭代清单!$H$2:$H$20,"进行中")</f>
         <v>0</v>
       </c>
       <c r="E8" s="6" t="n">
-        <f aca="false">COUNTIFS(迭代清单!$B$2:$B$18,A8,迭代清单!$H$2:$H$18,"未开始")</f>
+        <f aca="false">COUNTIFS(迭代清单!$B$2:$B$20,A8,迭代清单!$H$2:$H$20,"未开始")</f>
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
@@ -1820,11 +1906,11 @@
       </c>
       <c r="B9" s="13" t="n">
         <f aca="false">SUM(B5:B8)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C9" s="13" t="n">
         <f aca="false">SUM(C5:C8)</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D9" s="13" t="n">
         <f aca="false">SUM(D5:D8)</f>
@@ -1832,11 +1918,11 @@
       </c>
       <c r="E9" s="13" t="n">
         <f aca="false">SUM(E5:E8)</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F9" s="14" t="n">
         <f aca="false">IF(B9=0,"",C9/B9)</f>
-        <v>0.235294117647059</v>
+        <v>0.473684210526316</v>
       </c>
       <c r="G9" s="12"/>
     </row>
@@ -1932,7 +2018,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -2186,12 +2272,18 @@
         <v>73</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I7" s="24"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="24"/>
+      <c r="J7" s="25" t="n">
+        <v>46316</v>
+      </c>
+      <c r="K7" s="25" t="n">
+        <v>46316</v>
+      </c>
+      <c r="L7" s="24" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="28" t="n">
@@ -2201,27 +2293,33 @@
         <v>68</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I8" s="24"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="24"/>
+      <c r="J8" s="25" t="n">
+        <v>46316</v>
+      </c>
+      <c r="K8" s="25" t="n">
+        <v>46316</v>
+      </c>
+      <c r="L8" s="24" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="n">
@@ -2231,27 +2329,33 @@
         <v>68</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G9" s="22" t="s">
         <v>19</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I9" s="24"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="24"/>
+      <c r="J9" s="25" t="n">
+        <v>46316</v>
+      </c>
+      <c r="K9" s="25" t="n">
+        <v>46316</v>
+      </c>
+      <c r="L9" s="24" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="n">
@@ -2261,49 +2365,55 @@
         <v>68</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I10" s="24"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="24"/>
+      <c r="J10" s="25" t="n">
+        <v>46316</v>
+      </c>
+      <c r="K10" s="25" t="n">
+        <v>46316</v>
+      </c>
+      <c r="L10" s="24" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H11" s="23" t="s">
         <v>6</v>
@@ -2318,22 +2428,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E12" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="G12" s="27" t="s">
         <v>94</v>
-      </c>
-      <c r="F12" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="G12" s="27" t="s">
-        <v>90</v>
       </c>
       <c r="H12" s="23" t="s">
         <v>6</v>
@@ -2348,22 +2458,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E13" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="F13" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="F13" s="22" t="s">
-        <v>92</v>
-      </c>
       <c r="G13" s="27" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H13" s="23" t="s">
         <v>6</v>
@@ -2378,22 +2488,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G14" s="27" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H14" s="23" t="s">
         <v>6</v>
@@ -2408,22 +2518,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H15" s="23" t="s">
         <v>6</v>
@@ -2441,22 +2551,22 @@
         <v>15</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G16" s="27" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H16" s="23" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I16" s="24"/>
       <c r="J16" s="25"/>
@@ -2471,22 +2581,22 @@
         <v>15</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I17" s="24"/>
       <c r="J17" s="25"/>
@@ -2501,49 +2611,115 @@
         <v>15</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G18" s="27" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H18" s="23" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I18" s="24"/>
       <c r="J18" s="25"/>
       <c r="K18" s="25"/>
       <c r="L18" s="24"/>
     </row>
+    <row r="19" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="28" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="F19" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="G19" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="I19" s="24"/>
+      <c r="J19" s="25" t="n">
+        <v>46316</v>
+      </c>
+      <c r="K19" s="25" t="n">
+        <v>46316</v>
+      </c>
+      <c r="L19" s="24" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="30" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="G20" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="I20" s="24"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="24"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L18"/>
-  <conditionalFormatting sqref="H2:H18">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+  <autoFilter ref="A1:L20"/>
+  <conditionalFormatting sqref="H2:H20">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>"已完成"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>"进行中"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K18">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+  <conditionalFormatting sqref="K2:K20">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>AND(K2&lt;&gt;"",K2&lt;TODAY(),$H2&lt;&gt;"已完成",$H2&lt;&gt;"搁置")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" error="请从下拉列表选择：未开始、进行中、已完成、搁置" errorStyle="stop" errorTitle="状态" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:H18" type="list">
+    <dataValidation allowBlank="true" error="请从下拉列表选择：未开始、进行中、已完成、搁置" errorStyle="stop" errorTitle="状态" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:H20" type="list">
       <formula1>"未开始,进行中,已完成,搁置"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="请填写日期，例如 2026-11-02" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J2:K18" type="date">
+    <dataValidation allowBlank="true" error="请填写日期，例如 2026-11-02" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J2:K20" type="date">
       <formula1>DATE(2020,1,1)</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2580,34 +2756,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="F1" s="19" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="I1" s="19" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="J1" s="19" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="K1" s="19" t="s">
         <v>36</v>
@@ -2615,25 +2791,25 @@
     </row>
     <row r="2" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="22" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="E2" s="33" t="s">
-        <v>122</v>
-      </c>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="35" t="str">
+        <v>134</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="37" t="str">
         <f aca="false">IF(OR(F2="",H2=""),"",H2-F2)</f>
         <v/>
       </c>
@@ -2641,25 +2817,25 @@
     </row>
     <row r="3" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="22" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="E3" s="36" t="s">
-        <v>126</v>
-      </c>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="38" t="str">
+        <v>138</v>
+      </c>
+      <c r="E3" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="40" t="str">
         <f aca="false">IF(OR(F3="",H3=""),"",H3-F3)</f>
         <v/>
       </c>
@@ -2667,25 +2843,25 @@
     </row>
     <row r="4" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="22" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>73</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>122</v>
-      </c>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="35" t="str">
+        <v>142</v>
+      </c>
+      <c r="E4" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="37" t="str">
         <f aca="false">IF(OR(F4="",H4=""),"",H4-F4)</f>
         <v/>
       </c>
@@ -2693,25 +2869,25 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="E5" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="40" t="str">
+        <v>145</v>
+      </c>
+      <c r="E5" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="42" t="str">
         <f aca="false">IF(OR(F5="",H5=""),"",H5-F5)</f>
         <v/>
       </c>
@@ -2719,25 +2895,25 @@
     </row>
     <row r="6" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="E6" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="38" t="str">
+        <v>150</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="40" t="str">
         <f aca="false">IF(OR(F6="",H6=""),"",H6-F6)</f>
         <v/>
       </c>
@@ -2745,23 +2921,23 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="41" t="s">
-        <v>139</v>
-      </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="41"/>
+      <c r="A9" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
